--- a/10. Sistemas de gestion empresarial/NumeroDiasAusentado.xlsx
+++ b/10. Sistemas de gestion empresarial/NumeroDiasAusentado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheng\Desktop\2DAM\10. Sistemas de gestion empresarial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF61E54-D26C-4CB1-A481-835BFAAF3A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2B7076-AE07-4C7B-8634-65BD230350A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
   </si>
   <si>
     <t>diciembre 2025</t>
-  </si>
-  <si>
-    <t>Duración (días)</t>
   </si>
   <si>
     <t>Número</t>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">               Marc Demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -175,7 +175,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Días ausentados</a:t>
+              <a:t>Días ausentados Diciembre 2025</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -217,11 +217,11 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Resumen de ausencias'!$B$1:$B$3</c:f>
+              <c:f>'Resumen de ausencias'!$C$1:$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -231,14 +231,14 @@
                   <c:v>diciembre 2025</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Duración (días)</c:v>
+                  <c:v>Número</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -255,31 +255,28 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Resumen de ausencias'!$A$4,'Resumen de ausencias'!$A$7,'Resumen de ausencias'!$A$9:$A$10,'Resumen de ausencias'!$A$12,'Resumen de ausencias'!$A$15,'Resumen de ausencias'!$A$18,'Resumen de ausencias'!$A$20)</c:f>
+              <c:f>('Resumen de ausencias'!$A$7,'Resumen de ausencias'!$A$9:$A$10,'Resumen de ausencias'!$A$12,'Resumen de ausencias'!$A$15,'Resumen de ausencias'!$A$18,'Resumen de ausencias'!$A$20)</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>               Sharlene Rhodes</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>               Mitchell Admin</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>               Sharlene Rhodes</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>               Mitchell Admin</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>               Sharlene Rhodes</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>               Mitchell Admin</c:v>
+                  <c:v>               Anita Oliver</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>               Anita Oliver</c:v>
+                  <c:v>               Ronnie Hart</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>               Ronnie Hart</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>               Marc Demo</c:v>
                 </c:pt>
               </c:strCache>
@@ -294,43 +291,452 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Resumen de ausencias'!$B$4,'Resumen de ausencias'!$B$7,'Resumen de ausencias'!$B$9:$B$10,'Resumen de ausencias'!$B$12,'Resumen de ausencias'!$B$15,'Resumen de ausencias'!$B$18,'Resumen de ausencias'!$B$20)</c:f>
+              <c:f>('Resumen de ausencias'!$B$7,'Resumen de ausencias'!$B$9:$B$10,'Resumen de ausencias'!$B$12,'Resumen de ausencias'!$B$15,'Resumen de ausencias'!$B$18,'Resumen de ausencias'!$B$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>31</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-094F-4FFC-948D-FAAE6DD493CA}"/>
+              <c16:uniqueId val="{00000001-094F-4FFC-948D-FAAE6DD493CA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="499382400"/>
+        <c:axId val="499383232"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Resumen de ausencias'!$B$1:$B$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>Total</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>diciembre 2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'Resumen de ausencias'!$A$4:$A$20</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>('Resumen de ausencias'!$A$7,'Resumen de ausencias'!$A$9:$A$10,'Resumen de ausencias'!$A$12,'Resumen de ausencias'!$A$15,'Resumen de ausencias'!$A$18,'Resumen de ausencias'!$A$20)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="7"/>
+                      <c:pt idx="0">
+                        <c:v>     Administración</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>               Sharlene Rhodes</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>          Ausencias por enfermedad</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>               Mitchell Admin</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>               Sharlene Rhodes</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>          Días compensatorios</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>               Mitchell Admin</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU.</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>               Anita Oliver</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>     Administración / Investigación y desarrollo</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>               Ronnie Hart</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>          Ausencias por enfermedad</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>               Marc Demo</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'Resumen de ausencias'!#REF!</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'Resumen de ausencias'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="0"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-094F-4FFC-948D-FAAE6DD493CA}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="499382400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="499383232"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="499383232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="499382400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Días ausentados por</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> departamento </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Diciembre</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 2025</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -370,32 +776,17 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Resumen de ausencias'!$A$4,'Resumen de ausencias'!$A$7,'Resumen de ausencias'!$A$9:$A$10,'Resumen de ausencias'!$A$12,'Resumen de ausencias'!$A$15,'Resumen de ausencias'!$A$18,'Resumen de ausencias'!$A$20)</c:f>
+              <c:f>('Resumen de ausencias'!$A$5,'Resumen de ausencias'!$A$13,'Resumen de ausencias'!$A$16)</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>     Administración</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>               Sharlene Rhodes</c:v>
+                  <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU.</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>               Mitchell Admin</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>               Sharlene Rhodes</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>               Mitchell Admin</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>               Anita Oliver</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>               Ronnie Hart</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>               Marc Demo</c:v>
+                  <c:v>     Administración / Investigación y desarrollo</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -405,44 +796,29 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Resumen de ausencias'!$C$4:$C$20</c15:sqref>
+                    <c15:sqref>'Resumen de ausencias'!$B$4:$B$20</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Resumen de ausencias'!$C$4,'Resumen de ausencias'!$C$7,'Resumen de ausencias'!$C$9:$C$10,'Resumen de ausencias'!$C$12,'Resumen de ausencias'!$C$15,'Resumen de ausencias'!$C$18,'Resumen de ausencias'!$C$20)</c:f>
+              <c:f>('Resumen de ausencias'!$B$5,'Resumen de ausencias'!$B$13,'Resumen de ausencias'!$B$16)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-094F-4FFC-948D-FAAE6DD493CA}"/>
+              <c16:uniqueId val="{00000001-1B55-49B8-9B82-64C09C5E5758}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -457,6 +833,134 @@
         <c:gapWidth val="182"/>
         <c:axId val="499382400"/>
         <c:axId val="499383232"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Resumen de ausencias'!$B$1:$B$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>Total</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>diciembre 2025</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'Resumen de ausencias'!$A$4:$A$20</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>('Resumen de ausencias'!$A$5,'Resumen de ausencias'!$A$13,'Resumen de ausencias'!$A$16)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="3"/>
+                      <c:pt idx="0">
+                        <c:v>     Administración</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>               Sharlene Rhodes</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>          Ausencias por enfermedad</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>               Mitchell Admin</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>               Sharlene Rhodes</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>          Días compensatorios</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>               Mitchell Admin</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>     Administración / Investigación y desarrollo / I&amp;D EE. UU.</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>               Anita Oliver</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>     Administración / Investigación y desarrollo</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>          Ausencia pagada</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>               Ronnie Hart</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>          Ausencias por enfermedad</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>               Marc Demo</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>'Resumen de ausencias'!#REF!</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>'Resumen de ausencias'!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="0"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-1B55-49B8-9B82-64C09C5E5758}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
       </c:barChart>
       <c:catAx>
         <c:axId val="499382400"/>
@@ -681,7 +1185,552 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1219,6 +2268,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>33339</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2428A3D-1797-4874-9566-2D69863881EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1548,221 +2635,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6">
+      <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
+      <c r="B19">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16">
-        <v>8</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="38" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R38" t="s">
         <v>14</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
